--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513597_ELIMINATORIAS12FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513597_ELIMINATORIAS12FINAL_PROCESSED.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5273</v>
+        <v>3.2353</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4664</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9938</v>
+        <v>3.1634</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5822</v>
+        <v>1.616</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.4775</v>
+        <v>-2.4524</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0597</v>
+        <v>4.0684</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4076</v>
+        <v>1.5035</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.585</v>
+        <v>-1.5251</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9927</v>
+        <v>3.0286</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1746</v>
+        <v>0.1125</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8925</v>
+        <v>-0.9273</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0671</v>
+        <v>1.0397</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4582</v>
+        <v>-2.4294</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9694</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5965</v>
+        <v>-0.1924</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5659</v>
+        <v>0.824</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0057</v>
+        <v>2.8772</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6838</v>
+        <v>0.5632</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3219</v>
+        <v>2.314</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2422</v>
+        <v>-0.2598</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7248</v>
+        <v>-0.7311</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4826</v>
+        <v>0.4713</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.6629</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6129</v>
+        <v>-0.594</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.05</v>
+        <v>-0.0325</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4207</v>
+        <v>0.3667</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1119</v>
+        <v>-0.1371</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5326</v>
+        <v>0.5038</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7521</v>
+        <v>-0.863</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6048</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1472</v>
+        <v>-0.0772</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9957</v>
+        <v>0.952</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7948</v>
+        <v>1.0305</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2009</v>
+        <v>-0.0785</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8546</v>
+        <v>1.8708</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1099</v>
+        <v>1.1447</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7447</v>
+        <v>0.7261</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4239</v>
+        <v>1.4804</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3054</v>
+        <v>1.3611</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1185</v>
+        <v>0.1193</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4307</v>
+        <v>0.3904</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1954</v>
+        <v>-0.2164</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6261</v>
+        <v>0.6068</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2473</v>
+        <v>1.1744</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7062</v>
+        <v>0.858</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5412</v>
+        <v>0.3164</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2868</v>
+        <v>-1.2834</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1062</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0063</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2905</v>
+        <v>0.4696</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7158</v>
+        <v>0.4775</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3161</v>
+        <v>1.6716</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1143</v>
+        <v>-1.3248</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2018</v>
+        <v>2.9964</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0132</v>
+        <v>0.9701</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0528</v>
+        <v>-0.6743</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0395</v>
+        <v>1.6444</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3294</v>
+        <v>0.7015</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1671</v>
+        <v>-0.6504</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1623</v>
+        <v>1.352</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.4049</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0242</v>
+        <v>1.4172</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.334</v>
+        <v>0.0485</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3038</v>
+        <v>-0.6907</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6378</v>
+        <v>0.7392</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.7853</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5951</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.3804</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8606</v>
+        <v>0.8061</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.002</v>
+        <v>0.247</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8626</v>
+        <v>0.5591</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6585</v>
+        <v>3.0328</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3322</v>
+        <v>3.6938</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9907</v>
+        <v>-0.661</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8807</v>
+        <v>2.4898</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7184</v>
+        <v>3.8107</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5991</v>
+        <v>-1.3209</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7778</v>
+        <v>0.543</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6138</v>
+        <v>-0.1169</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3916</v>
+        <v>0.6599</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0242</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.4097</v>
+        <v>-1.6196</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4339</v>
+        <v>1.2147</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0513</v>
+        <v>-0.3807</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0633</v>
+        <v>-0.8741</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0121</v>
+        <v>0.4935</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7709</v>
+        <v>-1.4411</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5903</v>
+        <v>0.2509</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3612</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1996</v>
+        <v>0.6712</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7794</v>
+        <v>-0.1078</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5798</v>
+        <v>0.7789</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9964</v>
+        <v>0.3143</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6411</v>
+        <v>0.1184</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6447000000000001</v>
+        <v>0.1959</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3857</v>
+        <v>-0.0004</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7252</v>
+        <v>-0.0402</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3395</v>
+        <v>0.0398</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6107</v>
+        <v>0.3147</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.08409999999999999</v>
+        <v>0.1586</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6948</v>
+        <v>0.1561</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4097</v>
+        <v>1.0123</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.6388</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2291</v>
+        <v>1.0123</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3637</v>
+        <v>-0.6554</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.7684</v>
+        <v>-0.1074</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4047</v>
+        <v>-0.548</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4227</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2421</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.6647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7317</v>
+        <v>0.259</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6451</v>
+        <v>-0.9569</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9134</v>
+        <v>1.2159</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5826</v>
+        <v>0.4174</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1226</v>
+        <v>-0.9285</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7050999999999999</v>
+        <v>1.3459</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5729</v>
+        <v>0.6055</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6519</v>
+        <v>0.0579</v>
       </c>
       <c r="L8" t="n">
-        <v>0.079</v>
+        <v>0.5476</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1555</v>
+        <v>-0.1881</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5294</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6261</v>
+        <v>0.7983</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2048</v>
+        <v>0.8098</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.4339</v>
+        <v>-0.4049</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1094</v>
+        <v>-0.2799</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6383</v>
+        <v>-0.4692</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4711</v>
+        <v>0.1893</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6883</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6883</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-0.1597</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9161</v>
+        <v>-2.2793</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0023</v>
+        <v>2.1196</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4347</v>
+        <v>0.5675</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9172</v>
+        <v>-0.1188</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3519</v>
+        <v>0.6863</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5488</v>
+        <v>-0.554</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0311</v>
+        <v>-0.6335</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5177</v>
+        <v>0.0795</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1141</v>
+        <v>1.1215</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9483</v>
+        <v>0.5147</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.6068</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8194</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.4097</v>
+        <v>-1.4172</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4714</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3587</v>
+        <v>-0.3082</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1127</v>
+        <v>-0.2166</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6965</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6965</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.437</v>
+        <v>-1.0178</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.096</v>
+        <v>-0.8731</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.341</v>
+        <v>-0.1447</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3079</v>
+        <v>-0.3015</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0643</v>
+        <v>0.0784</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3722</v>
+        <v>-0.3798</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.134</v>
+        <v>-1.1083</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4373</v>
+        <v>-0.4162</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8068</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5016</v>
+        <v>0.4945</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3245</v>
+        <v>0.3122</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9242</v>
+        <v>-0.5139</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5895</v>
+        <v>-0.4084</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3347</v>
+        <v>-0.1054</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8324</v>
+        <v>0.846</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8324</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6326</v>
+        <v>-4.4126</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7638</v>
+        <v>-3.5169</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8688</v>
+        <v>-0.8956</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6026</v>
+        <v>-3.6061</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1651</v>
+        <v>-1.1662</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4375</v>
+        <v>-2.4399</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.2481</v>
+        <v>-3.2227</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2764</v>
+        <v>-1.2657</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9717</v>
+        <v>-1.957</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3545</v>
+        <v>-0.3834</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1113</v>
+        <v>0.0994</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4658</v>
+        <v>-0.4829</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2833</v>
+        <v>-1.0334</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.2943</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7677</v>
+        <v>-0.7392</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.4809</v>
+        <v>4.157800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.899699999999999</v>
+        <v>-5.351800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>10.3807</v>
+        <v>9.509600000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>5.2724</v>
+        <v>5.322999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.809800000000001</v>
+        <v>-1.6865</v>
       </c>
       <c r="I12" t="n">
-        <v>7.082100000000001</v>
+        <v>7.009600000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0156</v>
+        <v>1.537399999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2729999999999997</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2885</v>
+        <v>1.4567</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2569</v>
+        <v>3.785600000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5366</v>
+        <v>-1.7673</v>
       </c>
       <c r="O12" t="n">
-        <v>5.7935</v>
+        <v>5.5527</v>
       </c>
       <c r="P12" t="n">
-        <v>4.097</v>
+        <v>4.048999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.193900000000001</v>
+        <v>-8.098100000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>12.2908</v>
+        <v>12.1472</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.0727</v>
+        <v>-2.3965</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.1251</v>
+        <v>-3.2725</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0527</v>
+        <v>0.876</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.8157</v>
+        <v>-2.8177</v>
       </c>
       <c r="W12" t="n">
-        <v>4.4039</v>
+        <v>4.4811</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.2195</v>
+        <v>-7.2989</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8715</v>
+        <v>6.4227</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1751</v>
+        <v>5.8275</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6963</v>
+        <v>0.5952</v>
       </c>
       <c r="G13" t="n">
-        <v>6.0079</v>
+        <v>6.026</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5621</v>
+        <v>3.5583</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4457</v>
+        <v>2.4677</v>
       </c>
       <c r="J13" t="n">
-        <v>6.8697</v>
+        <v>6.9629</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9811</v>
+        <v>4.03</v>
       </c>
       <c r="L13" t="n">
-        <v>2.8886</v>
+        <v>2.9329</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8618</v>
+        <v>-0.9369</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4189</v>
+        <v>-0.4717</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4429</v>
+        <v>-0.4651</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0684</v>
+        <v>0.5991</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6703</v>
+        <v>-0.1232</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7388</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.476</v>
+        <v>2.1521</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9298</v>
+        <v>-0.9447</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4057</v>
+        <v>3.0968</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3518</v>
+        <v>0.3397</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1619</v>
+        <v>-0.1771</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5137</v>
+        <v>0.5168</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7805</v>
+        <v>-0.7453</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.673</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0895</v>
+        <v>-0.0723</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1323</v>
+        <v>1.085</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5291</v>
+        <v>0.4959</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6032</v>
+        <v>0.5891</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2471</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5477</v>
+        <v>-0.6283</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7948</v>
+        <v>0.5622</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8771</v>
+        <v>1.8785</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4544</v>
+        <v>0.4374</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0719</v>
+        <v>0.6687</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1668</v>
+        <v>-0.2658</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2387</v>
+        <v>0.9345</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.0354</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5862</v>
+        <v>0.3962</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4492</v>
+        <v>-0.9631</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.6197</v>
+        <v>-0.7811</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.056</v>
+        <v>0.079</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5637</v>
+        <v>-0.8601</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4157</v>
+        <v>0.2141</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5302</v>
+        <v>0.3171</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1145</v>
+        <v>-0.103</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0242</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0242</v>
+        <v>0.4049</v>
       </c>
       <c r="S15" t="n">
-        <v>2.083</v>
+        <v>0.6528</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4528</v>
+        <v>0.3373</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6302</v>
+        <v>0.3155</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6768</v>
+        <v>0.5485</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3723</v>
+        <v>-0.5517</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0491</v>
+        <v>1.1002</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1331</v>
+        <v>0.1153</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8309</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7113</v>
+        <v>-0.7156</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5534</v>
+        <v>-0.5342</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0643</v>
+        <v>0.0784</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6177</v>
+        <v>-0.6126</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6865</v>
+        <v>0.6495</v>
       </c>
       <c r="N16" t="n">
-        <v>0.78</v>
+        <v>0.7526</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0935</v>
+        <v>-0.103</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5567</v>
+        <v>0.4694</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1811</v>
+        <v>-0.0174</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3756</v>
+        <v>0.4868</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8324</v>
+        <v>-0.846</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8324</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5363</v>
+        <v>0.3125</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6832</v>
+        <v>0.6048</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1469</v>
+        <v>-0.2923</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6136</v>
+        <v>-1.6453</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2435</v>
+        <v>-1.2641</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3702</v>
+        <v>-0.3813</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5392</v>
+        <v>-0.5333</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6577</v>
+        <v>-0.6526</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1185</v>
+        <v>0.1193</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0744</v>
+        <v>-1.112</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5857</v>
+        <v>-0.6115</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4887</v>
+        <v>-0.5006</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2114</v>
+        <v>0.0186</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0418</v>
+        <v>-0.052</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1696</v>
+        <v>0.0706</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5288</v>
+        <v>1.5344</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3482</v>
+        <v>0.3442</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0236</v>
+        <v>0.1467</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.844</v>
+        <v>-1.6222</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8676</v>
+        <v>1.7688</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5716</v>
+        <v>-2.0612</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4123</v>
+        <v>-1.6004</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9838</v>
+        <v>-0.4608</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8122</v>
+        <v>-1.5786</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0781</v>
+        <v>-1.0293</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.8903</v>
+        <v>-0.5493</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2407</v>
+        <v>-0.4826</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3342</v>
+        <v>-0.5712</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0935</v>
+        <v>0.0885</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6145</v>
+        <v>1.0123</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4097</v>
+        <v>1.0123</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0291</v>
+        <v>1.1956</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1881</v>
+        <v>-0.0436</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2173</v>
+        <v>1.2392</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7744</v>
+        <v>-1.0684</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0261</v>
+        <v>-2.33</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7483</v>
+        <v>1.2616</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8537</v>
+        <v>-0.751</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0924</v>
+        <v>1.0293</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7613</v>
+        <v>-1.7803</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1195</v>
+        <v>-1.9542</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2985</v>
+        <v>0.1383</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.179</v>
+        <v>-2.0925</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9731</v>
+        <v>1.2032</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3909</v>
+        <v>0.891</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5822000000000001</v>
+        <v>0.3122</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6145</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4097</v>
+        <v>1.0123</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2841</v>
+        <v>0.0268</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2884</v>
+        <v>-0.2095</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0043</v>
+        <v>0.2364</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5903</v>
+        <v>-0.3442</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5903</v>
+        <v>0.846</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2121</v>
+        <v>-1.3468</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.022</v>
+        <v>-0.0441</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8099</v>
+        <v>-1.3028</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7348</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>1.056</v>
+        <v>-0.1173</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7908</v>
+        <v>-0.7481</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9787</v>
+        <v>0.1709</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1366</v>
+        <v>0.3154</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.1153</v>
+        <v>-0.1445</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2439</v>
+        <v>-1.0363</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9194</v>
+        <v>-0.4327</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3245</v>
+        <v>-0.6036</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0242</v>
+        <v>0.4049</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.129</v>
+        <v>0.721</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8515</v>
+        <v>0.2022</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2776</v>
+        <v>0.5189</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3482</v>
+        <v>-0.5951</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8324</v>
+        <v>0.5951</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0517</v>
+        <v>-4.6546</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8173</v>
+        <v>-5.1636</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2344</v>
+        <v>0.509</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1565</v>
+        <v>-2.7621</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5351</v>
+        <v>-1.503</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.6917</v>
+        <v>-1.2591</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.8853</v>
+        <v>-1.9636</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4799</v>
+        <v>-1.0313</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.3652</v>
+        <v>-0.9324</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2712</v>
+        <v>-0.7985</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0552</v>
+        <v>-0.4717</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3264</v>
+        <v>-0.3267</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0485</v>
+        <v>-2.8343</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0727</v>
+        <v>-4.049</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0242</v>
+        <v>1.2147</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3339</v>
+        <v>-0.2484</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5504</v>
+        <v>-0.5921</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7835</v>
+        <v>0.3437</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5903</v>
+        <v>1.4411</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7709</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0988</v>
+        <v>-5.3145</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.0607</v>
+        <v>-5.0199</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0381</v>
+        <v>-0.2946</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7995</v>
+        <v>-3.1518</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5161</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2834</v>
+        <v>-3.6856</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.077</v>
+        <v>-2.8289</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0972</v>
+        <v>0.5123</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9798</v>
+        <v>-3.3412</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7225</v>
+        <v>-0.3229</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4189</v>
+        <v>0.0215</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3035</v>
+        <v>-0.3444</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.8679</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.097</v>
+        <v>-3.0368</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2291</v>
+        <v>1.0123</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6121</v>
+        <v>1.052</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3094</v>
+        <v>0.2507</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3026</v>
+        <v>0.8014</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4227</v>
+        <v>0.5951</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2421</v>
+        <v>-1.7853</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.480900000000001</v>
+        <v>-2.1331</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.3807</v>
+        <v>-9.509699999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>6.8996</v>
+        <v>7.3764</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.2723</v>
+        <v>-5.322800000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8097</v>
+        <v>1.6866</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.0823</v>
+        <v>-7.0094</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.2568</v>
+        <v>-3.7854</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5366</v>
+        <v>1.7672</v>
       </c>
       <c r="L23" t="n">
-        <v>-5.7934</v>
+        <v>-5.5527</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0153</v>
+        <v>-1.5374</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2733</v>
+        <v>-0.08069999999999997</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2885</v>
+        <v>-1.4566</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.096900000000001</v>
+        <v>-4.0491</v>
       </c>
       <c r="Q23" t="n">
-        <v>-12.2907</v>
+        <v>-12.1473</v>
       </c>
       <c r="R23" t="n">
-        <v>8.193800000000001</v>
+        <v>8.0982</v>
       </c>
       <c r="S23" t="n">
-        <v>3.0726</v>
+        <v>4.4208</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0525</v>
+        <v>-0.8758999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>4.1253</v>
+        <v>5.297000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>2.8156</v>
+        <v>2.8178</v>
       </c>
       <c r="W23" t="n">
-        <v>7.2196</v>
+        <v>7.2988</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.404</v>
+        <v>-4.481</v>
       </c>
     </row>
   </sheetData>
